--- a/Bill of Materials/HackroDevX BOM.xlsx
+++ b/Bill of Materials/HackroDevX BOM.xlsx
@@ -1,26 +1,93 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hack Club Projects\Forge\HackroDevX\Bill of Materials\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F31B511A-A342-4C67-AD56-9F5D8E8D138F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+  <si>
+    <t>Component Category</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Side Note</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>PCBA</t>
+  </si>
+  <si>
+    <t>PCB [5]</t>
+  </si>
+  <si>
+    <t>No assembly</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>E-POST Shipping</t>
+  </si>
+  <si>
+    <t>Cheapest Option</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>HackroDevX BOM</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+  </numFmts>
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +95,136 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="30"/>
+      <color theme="1"/>
+      <name val="Bahnschrift SemiBold Condensed"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Bahnschrift SemiBold Condensed"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Bahnschrift SemiBold Condensed"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Bahnschrift SemiBold Condensed"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Bahnschrift SemiBold Condensed"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Bahnschrift SemiBold Condensed"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -45,14 +232,107 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -330,10 +610,164 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="255.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="36.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="9">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="10"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="7"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="10"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="7"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="10"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="7"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="10"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="7"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="10"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="7"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="10"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="7"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="10"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="7"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="10"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="7"/>
+      <c r="B11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="12">
+        <f>SUM(C3:C10)</f>
+        <v>16.399999999999999</v>
+      </c>
+      <c r="D11" s="12"/>
+      <c r="E11" s="13"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="16"/>
+      <c r="B12" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="9">
+        <v>16.73</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="14"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="17"/>
+      <c r="B13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="12">
+        <f>SUM(C12:C12)</f>
+        <v>16.73</v>
+      </c>
+      <c r="D13" s="12"/>
+      <c r="E13" s="15"/>
+    </row>
+    <row r="14" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="18"/>
+      <c r="C14" s="19" t="e">
+        <f>SUM(C11,#REF!,C13)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A3:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="D14:E14"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>